--- a/crates/unluminous-sheet/_agent_output/pivot/explore/exp1/edge_f_stdevp.xlsx
+++ b/crates/unluminous-sheet/_agent_output/pivot/explore/exp1/edge_f_stdevp.xlsx
@@ -690,7 +690,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Val" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsMixedTypes="1" containsNumber="1" minValue="-10" maxValue="20" count="10">
+      <sharedItems containsString="0" containsMixedTypes="1" containsNumber="1" minValue="-10" maxValue="20" count="10">
         <n v="10"/>
         <n v="-10"/>
         <n v="0"/>
